--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/PrjFeeAllotmentTemplate.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/PrjFeeAllotmentTemplate.xlsx
@@ -353,7 +353,7 @@
     <t>{data1.cashierPaymentAmount}</t>
   </si>
   <si>
-    <t>{data1.attachments}</t>
+    <t>{data1.fileName}</t>
   </si>
   <si>
     <t>发票金额合计</t>
